--- a/data/hole/data.xlsx
+++ b/data/hole/data.xlsx
@@ -486,7 +486,7 @@
         <v>133.95952333</v>
       </c>
       <c r="D3" t="str">
-        <v>高松国分寺ホール</v>
+        <v>朝日段ボールホール国分寺（高松国分寺ホール）</v>
       </c>
       <c r="E3" t="str">
         <v>高松市国分寺町新名430</v>

--- a/data/hole/data.xlsx
+++ b/data/hole/data.xlsx
@@ -457,7 +457,7 @@
         <v>087-825-5000</v>
       </c>
       <c r="G2" t="str">
-        <v>http://www.sunport-hall.jp/</v>
+        <v>https://www.sunport-hall.jp/</v>
       </c>
       <c r="H2" t="str">
         <v/>
@@ -495,7 +495,7 @@
         <v>087-875-0162</v>
       </c>
       <c r="G3" t="str">
-        <v>http://kokubunji-hall.jp/</v>
+        <v>https://kokubunji-hall.jp/</v>
       </c>
       <c r="H3" t="str">
         <v/>
